--- a/docs/QMS_관리항목_기준정의서.xlsx
+++ b/docs/QMS_관리항목_기준정의서.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구축로드맵" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'관리항목'!$A$1:$V$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'관리항목'!$A$1:$V$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'원인진단_지식베이스'!$A$1:$K$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>작성: 품질관리팀 · 생성일 2026-10-27 · 시스템 설정(qms/standards.py, qms/knowledge.py)에서 자동 생성</t>
+          <t>작성: 품질관리팀 · 생성일 2026-10-28 · 시스템 설정(qms/standards.py, qms/knowledge.py)에서 자동 생성</t>
         </is>
       </c>
     </row>
@@ -746,23 +746,23 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTIF(관리항목!$B$2:$B$81,A4)</f>
+        <f>COUNTIF(관리항목!$B$2:$B$84,A4)</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A4,관리항목!$J$2:$J$81,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$81,A4,관리항목!$J$2:$J$81,"",관리항목!$K$2:$K$81,"&lt;&gt;")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A4,관리항목!$J$2:$J$84,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$84,A4,관리항목!$J$2:$J$84,"",관리항목!$K$2:$K$84,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A4,관리항목!$U$2:$U$81,"●")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A4,관리항목!$U$2:$U$84,"●")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A4,관리항목!$T$2:$T$81,"&lt;&gt;-")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A4,관리항목!$T$2:$T$84,"&lt;&gt;-")</f>
         <v/>
       </c>
       <c r="F4" s="10">
-        <f>SUMPRODUCT((관리항목!$B$2:$B$81=A4)*((LEN(관리항목!$Q$2:$Q$81)+LEN(관리항목!$R$2:$R$81)+LEN(관리항목!$S$2:$S$81))&gt;0))</f>
+        <f>SUMPRODUCT((관리항목!$B$2:$B$84=A4)*((LEN(관리항목!$Q$2:$Q$84)+LEN(관리항목!$R$2:$R$84)+LEN(관리항목!$S$2:$S$84))&gt;0))</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -777,23 +777,23 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(관리항목!$B$2:$B$81,A5)</f>
+        <f>COUNTIF(관리항목!$B$2:$B$84,A5)</f>
         <v/>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A5,관리항목!$J$2:$J$81,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$81,A5,관리항목!$J$2:$J$81,"",관리항목!$K$2:$K$81,"&lt;&gt;")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A5,관리항목!$J$2:$J$84,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$84,A5,관리항목!$J$2:$J$84,"",관리항목!$K$2:$K$84,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A5,관리항목!$U$2:$U$81,"●")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A5,관리항목!$U$2:$U$84,"●")</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A5,관리항목!$T$2:$T$81,"&lt;&gt;-")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A5,관리항목!$T$2:$T$84,"&lt;&gt;-")</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>SUMPRODUCT((관리항목!$B$2:$B$81=A5)*((LEN(관리항목!$Q$2:$Q$81)+LEN(관리항목!$R$2:$R$81)+LEN(관리항목!$S$2:$S$81))&gt;0))</f>
+        <f>SUMPRODUCT((관리항목!$B$2:$B$84=A5)*((LEN(관리항목!$Q$2:$Q$84)+LEN(관리항목!$R$2:$R$84)+LEN(관리항목!$S$2:$S$84))&gt;0))</f>
         <v/>
       </c>
       <c r="G5" s="11">
@@ -808,23 +808,23 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(관리항목!$B$2:$B$81,A6)</f>
+        <f>COUNTIF(관리항목!$B$2:$B$84,A6)</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A6,관리항목!$J$2:$J$81,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$81,A6,관리항목!$J$2:$J$81,"",관리항목!$K$2:$K$81,"&lt;&gt;")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A6,관리항목!$J$2:$J$84,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$84,A6,관리항목!$J$2:$J$84,"",관리항목!$K$2:$K$84,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A6,관리항목!$U$2:$U$81,"●")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A6,관리항목!$U$2:$U$84,"●")</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A6,관리항목!$T$2:$T$81,"&lt;&gt;-")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A6,관리항목!$T$2:$T$84,"&lt;&gt;-")</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>SUMPRODUCT((관리항목!$B$2:$B$81=A6)*((LEN(관리항목!$Q$2:$Q$81)+LEN(관리항목!$R$2:$R$81)+LEN(관리항목!$S$2:$S$81))&gt;0))</f>
+        <f>SUMPRODUCT((관리항목!$B$2:$B$84=A6)*((LEN(관리항목!$Q$2:$Q$84)+LEN(관리항목!$R$2:$R$84)+LEN(관리항목!$S$2:$S$84))&gt;0))</f>
         <v/>
       </c>
       <c r="G6" s="11">
@@ -839,23 +839,23 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(관리항목!$B$2:$B$81,A7)</f>
+        <f>COUNTIF(관리항목!$B$2:$B$84,A7)</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A7,관리항목!$J$2:$J$81,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$81,A7,관리항목!$J$2:$J$81,"",관리항목!$K$2:$K$81,"&lt;&gt;")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A7,관리항목!$J$2:$J$84,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$84,A7,관리항목!$J$2:$J$84,"",관리항목!$K$2:$K$84,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A7,관리항목!$U$2:$U$81,"●")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A7,관리항목!$U$2:$U$84,"●")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A7,관리항목!$T$2:$T$81,"&lt;&gt;-")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A7,관리항목!$T$2:$T$84,"&lt;&gt;-")</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>SUMPRODUCT((관리항목!$B$2:$B$81=A7)*((LEN(관리항목!$Q$2:$Q$81)+LEN(관리항목!$R$2:$R$81)+LEN(관리항목!$S$2:$S$81))&gt;0))</f>
+        <f>SUMPRODUCT((관리항목!$B$2:$B$84=A7)*((LEN(관리항목!$Q$2:$Q$84)+LEN(관리항목!$R$2:$R$84)+LEN(관리항목!$S$2:$S$84))&gt;0))</f>
         <v/>
       </c>
       <c r="G7" s="11">
@@ -870,23 +870,23 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(관리항목!$B$2:$B$81,A8)</f>
+        <f>COUNTIF(관리항목!$B$2:$B$84,A8)</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A8,관리항목!$J$2:$J$81,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$81,A8,관리항목!$J$2:$J$81,"",관리항목!$K$2:$K$81,"&lt;&gt;")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A8,관리항목!$J$2:$J$84,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$84,A8,관리항목!$J$2:$J$84,"",관리항목!$K$2:$K$84,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A8,관리항목!$U$2:$U$81,"●")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A8,관리항목!$U$2:$U$84,"●")</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A8,관리항목!$T$2:$T$81,"&lt;&gt;-")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A8,관리항목!$T$2:$T$84,"&lt;&gt;-")</f>
         <v/>
       </c>
       <c r="F8" s="10">
-        <f>SUMPRODUCT((관리항목!$B$2:$B$81=A8)*((LEN(관리항목!$Q$2:$Q$81)+LEN(관리항목!$R$2:$R$81)+LEN(관리항목!$S$2:$S$81))&gt;0))</f>
+        <f>SUMPRODUCT((관리항목!$B$2:$B$84=A8)*((LEN(관리항목!$Q$2:$Q$84)+LEN(관리항목!$R$2:$R$84)+LEN(관리항목!$S$2:$S$84))&gt;0))</f>
         <v/>
       </c>
       <c r="G8" s="11">
@@ -901,23 +901,23 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>COUNTIF(관리항목!$B$2:$B$81,A9)</f>
+        <f>COUNTIF(관리항목!$B$2:$B$84,A9)</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A9,관리항목!$J$2:$J$81,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$81,A9,관리항목!$J$2:$J$81,"",관리항목!$K$2:$K$81,"&lt;&gt;")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A9,관리항목!$J$2:$J$84,"&lt;&gt;")+COUNTIFS(관리항목!$B$2:$B$84,A9,관리항목!$J$2:$J$84,"",관리항목!$K$2:$K$84,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A9,관리항목!$U$2:$U$81,"●")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A9,관리항목!$U$2:$U$84,"●")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS(관리항목!$B$2:$B$81,A9,관리항목!$T$2:$T$81,"&lt;&gt;-")</f>
+        <f>COUNTIFS(관리항목!$B$2:$B$84,A9,관리항목!$T$2:$T$84,"&lt;&gt;-")</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>SUMPRODUCT((관리항목!$B$2:$B$81=A9)*((LEN(관리항목!$Q$2:$Q$81)+LEN(관리항목!$R$2:$R$81)+LEN(관리항목!$S$2:$S$81))&gt;0))</f>
+        <f>SUMPRODUCT((관리항목!$B$2:$B$84=A9)*((LEN(관리항목!$Q$2:$Q$84)+LEN(관리항목!$R$2:$R$84)+LEN(관리항목!$S$2:$S$84))&gt;0))</f>
         <v/>
       </c>
       <c r="G9" s="11">
@@ -974,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3624,15 +3624,19 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>clk_lsf</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>클링커 LSF</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
+          <t>clk_cl</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>클링커 Cl</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2시간</t>
@@ -3660,18 +3664,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M36" s="15" t="n">
-        <v>93</v>
-      </c>
-      <c r="N36" s="15" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="O36" s="15" t="n">
-        <v>95</v>
-      </c>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>모니터링 항목(기준 미설정)</t>
         </is>
       </c>
       <c r="Q36" s="16" t="n"/>
@@ -3679,15 +3677,15 @@
       <c r="S36" s="16" t="n"/>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
-        </is>
-      </c>
-      <c r="U36" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U36" s="10" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>염소 — 바이패스·킬른 내 순환(코팅·링 형성) 지표</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -3700,15 +3698,19 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>clk_sm</t>
+          <t>clk_f</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>클링커 SM</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr"/>
+          <t>클링커 F</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2시간</t>
@@ -3736,18 +3738,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N37" s="15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O37" s="15" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="M37" s="15" t="n"/>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15" t="n"/>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>모니터링 항목(기준 미설정)</t>
         </is>
       </c>
       <c r="Q37" s="16" t="n"/>
@@ -3755,11 +3751,15 @@
       <c r="S37" s="16" t="n"/>
       <c r="T37" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U37" s="10" t="inlineStr"/>
-      <c r="V37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>불소 — 광화제. 과다 시 응결·초기강도 영향</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -3772,15 +3772,19 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>clk_im</t>
+          <t>clk_temp</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>클링커 IM</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
+          <t>클링커 온도</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2시간</t>
@@ -3808,18 +3812,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N38" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="M38" s="15" t="n"/>
+      <c r="N38" s="15" t="n"/>
+      <c r="O38" s="15" t="n"/>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>모니터링 항목(기준 미설정)</t>
         </is>
       </c>
       <c r="Q38" s="16" t="n"/>
@@ -3827,11 +3825,15 @@
       <c r="S38" s="16" t="n"/>
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U38" s="10" t="inlineStr"/>
-      <c r="V38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>냉각기 출구 클링커 온도(냉각 상태 지표)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -3844,19 +3846,15 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>clk_c3s</t>
+          <t>clk_lsf</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>클링커 C₃S(Bogue)</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>클링커 LSF</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2시간</t>
@@ -3885,13 +3883,13 @@
         </is>
       </c>
       <c r="M39" s="15" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="N39" s="15" t="n">
-        <v>63</v>
+        <v>97.5</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>57.5</v>
+        <v>95</v>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
@@ -3911,11 +3909,7 @@
           <t>●</t>
         </is>
       </c>
-      <c r="V39" s="4" t="inlineStr">
-        <is>
-          <t>28일 강도의 주 기여 광물. Bogue 계산값은 XRD 실측과 차이가 있음</t>
-        </is>
-      </c>
+      <c r="V39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -3928,19 +3922,15 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>clk_c3a</t>
+          <t>clk_sm</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>클링커 C₃A(Bogue)</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>클링커 SM</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2시간</t>
@@ -3968,11 +3958,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="15" t="n"/>
+      <c r="M40" s="15" t="n">
+        <v>2.3</v>
+      </c>
       <c r="N40" s="15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O40" s="15" t="n"/>
+        <v>2.7</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>2.5</v>
+      </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
           <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
@@ -3983,15 +3977,11 @@
       <c r="S40" s="16" t="n"/>
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R1, R2, R3, R5, R6</t>
         </is>
       </c>
       <c r="U40" s="10" t="inlineStr"/>
-      <c r="V40" s="4" t="inlineStr">
-        <is>
-          <t>초기 수화·응결·황산염 저항성에 영향</t>
-        </is>
-      </c>
+      <c r="V40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4004,19 +3994,15 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>clk_liquid</t>
+          <t>clk_im</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>액상량(1450℃)</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>클링커 IM</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2시간</t>
@@ -4045,13 +4031,13 @@
         </is>
       </c>
       <c r="M41" s="15" t="n">
-        <v>24</v>
+        <v>1.4</v>
       </c>
       <c r="N41" s="15" t="n">
-        <v>29</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>26.5</v>
+        <v>1.6</v>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
@@ -4063,7 +4049,7 @@
       <c r="S41" s="16" t="n"/>
       <c r="T41" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R1, R2, R3, R5, R6</t>
         </is>
       </c>
       <c r="U41" s="10" t="inlineStr"/>
@@ -4080,12 +4066,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>clk_na2oeq</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>클링커 등가알칼리</t>
+          <t>clk_c3s</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>클링커 C₃S(Bogue)</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4120,11 +4106,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M42" s="15" t="n"/>
+      <c r="M42" s="15" t="n">
+        <v>53</v>
+      </c>
       <c r="N42" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O42" s="15" t="n"/>
+        <v>63</v>
+      </c>
+      <c r="O42" s="15" t="n">
+        <v>57.5</v>
+      </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
           <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
@@ -4135,11 +4125,19 @@
       <c r="S42" s="16" t="n"/>
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="U42" s="10" t="inlineStr"/>
-      <c r="V42" s="4" t="inlineStr"/>
+          <t>R1, R2, R3, R5, R6</t>
+        </is>
+      </c>
+      <c r="U42" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>28일 강도의 주 기여 광물. Bogue 계산값은 XRD 실측과 차이가 있음</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4152,12 +4150,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>xrd_alite</t>
+          <t>clk_c3a</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>XRD 알라이트(C₃S)</t>
+          <t>클링커 C₃A(Bogue)</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4167,17 +4165,17 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>클링커 일일 시료(XRD·크롬, LIMS)</t>
+          <t>XRF·f-CaO·리터중량 시험</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>XRD-Rietveld 정량</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -4192,18 +4190,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="15" t="n">
-        <v>58</v>
-      </c>
+      <c r="M43" s="15" t="n"/>
       <c r="N43" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="O43" s="15" t="n">
-        <v>64</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="O43" s="15" t="n"/>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값(XRD-Rietveld 정량 기준) — 공장 기준으로 교체 필요</t>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q43" s="16" t="n"/>
@@ -4211,13 +4205,13 @@
       <c r="S43" s="16" t="n"/>
       <c r="T43" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="U43" s="10" t="inlineStr"/>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t>실측 C₃S. Bogue 계산값보다 통상 높게 나옴(고용 불순물 영향) — 강도 예측의 핵심 입력</t>
+          <t>초기 수화·응결·황산염 저항성에 영향</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4226,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>xrd_belite</t>
+          <t>clk_liquid</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>XRD 벨라이트(C₂S)</t>
+          <t>액상량(1450℃)</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4247,17 +4241,17 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>클링커 일일 시료(XRD·크롬, LIMS)</t>
+          <t>XRF·f-CaO·리터중량 시험</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>XRD-Rietveld 정량</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -4273,17 +4267,17 @@
         </is>
       </c>
       <c r="M44" s="15" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N44" s="15" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>14</v>
+        <v>26.5</v>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값(XRD-Rietveld 정량 기준) — 공장 기준으로 교체 필요</t>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q44" s="16" t="n"/>
@@ -4295,11 +4289,7 @@
         </is>
       </c>
       <c r="U44" s="10" t="inlineStr"/>
-      <c r="V44" s="4" t="inlineStr">
-        <is>
-          <t>장기강도(28일 이후) 기여 광물. 과다 시 조기강도 저하</t>
-        </is>
-      </c>
+      <c r="V44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -4312,12 +4302,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>xrd_c3a</t>
+          <t>clk_na2oeq</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>XRD C₃A(입방+사방)</t>
+          <t>클링커 등가알칼리</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4327,17 +4317,17 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>클링커 일일 시료(XRD·크롬, LIMS)</t>
+          <t>XRF·f-CaO·리터중량 시험</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>XRD-Rietveld 정량</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -4354,14 +4344,12 @@
       </c>
       <c r="M45" s="15" t="n"/>
       <c r="N45" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="O45" s="15" t="n">
-        <v>7.5</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="O45" s="15" t="n"/>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값(XRD-Rietveld 정량 기준) — 공장 기준으로 교체 필요</t>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q45" s="16" t="n"/>
@@ -4373,11 +4361,7 @@
         </is>
       </c>
       <c r="U45" s="10" t="inlineStr"/>
-      <c r="V45" s="4" t="inlineStr">
-        <is>
-          <t>초기 수화·응결 속도와 석고 요구량을 좌우</t>
-        </is>
-      </c>
+      <c r="V45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -4390,12 +4374,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>xrd_c4af</t>
+          <t>xrd_alite</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>XRD 페라이트(C₄AF)</t>
+          <t>XRD 알라이트(C₃S)</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4430,12 +4414,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M46" s="15" t="n"/>
-      <c r="N46" s="15" t="n"/>
-      <c r="O46" s="15" t="n"/>
+      <c r="M46" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="N46" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>64</v>
+      </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>모니터링 항목(기준 미설정)</t>
+          <t>경험칙 초기값(XRD-Rietveld 정량 기준) — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q46" s="16" t="n"/>
@@ -4443,11 +4433,15 @@
       <c r="S46" s="16" t="n"/>
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R1, R2, R3</t>
         </is>
       </c>
       <c r="U46" s="10" t="inlineStr"/>
-      <c r="V46" s="4" t="inlineStr"/>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>실측 C₃S. Bogue 계산값보다 통상 높게 나옴(고용 불순물 영향) — 강도 예측의 핵심 입력</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -4460,12 +4454,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>xrd_fcao</t>
+          <t>xrd_belite</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>XRD 자유석회</t>
+          <t>XRD 벨라이트(C₂S)</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4500,12 +4494,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" s="15" t="n"/>
+      <c r="M47" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="N47" s="15" t="n">
-        <v>1.8</v>
+        <v>20</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
@@ -4521,7 +4517,11 @@
         </is>
       </c>
       <c r="U47" s="10" t="inlineStr"/>
-      <c r="V47" s="4" t="inlineStr"/>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>장기강도(28일 이후) 기여 광물. 과다 시 조기강도 저하</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>xrd_periclase</t>
+          <t>xrd_c3a</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>XRD 페리클레이스(MgO)</t>
+          <t>XRD C₃A(입방+사방)</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4576,10 +4576,10 @@
       </c>
       <c r="M48" s="15" t="n"/>
       <c r="N48" s="15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
       <c r="U48" s="10" t="inlineStr"/>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>결정질 MgO. 과다 시 오토클레이브 팽창(안정도) 위험</t>
+          <t>초기 수화·응결 속도와 석고 요구량을 좌우</t>
         </is>
       </c>
     </row>
@@ -4612,17 +4612,17 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>clk_cr</t>
+          <t>xrd_c4af</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>클링커 총 크롬</t>
+          <t>XRD 페라이트(C₄AF)</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>XRF / ICP(총 크롬)</t>
+          <t>XRD-Rietveld 정량</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -4653,15 +4653,11 @@
         </is>
       </c>
       <c r="M49" s="15" t="n"/>
-      <c r="N49" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="O49" s="15" t="n">
-        <v>65</v>
-      </c>
+      <c r="N49" s="15" t="n"/>
+      <c r="O49" s="15" t="n"/>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>모니터링 항목(기준 미설정)</t>
         </is>
       </c>
       <c r="Q49" s="16" t="n"/>
@@ -4669,15 +4665,11 @@
       <c r="S49" s="16" t="n"/>
       <c r="T49" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U49" s="10" t="inlineStr"/>
-      <c r="V49" s="4" t="inlineStr">
-        <is>
-          <t>원·부원료·연료·내화물에서 유입된 크롬(XRF/ICP). 6가크롬의 모체</t>
-        </is>
-      </c>
+      <c r="V49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -4690,17 +4682,17 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>clk_crvi</t>
+          <t>xrd_fcao</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>클링커 수용성 Cr⁶⁺</t>
+          <t>XRD 자유석회</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -4715,7 +4707,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>KS L 5221 준용</t>
+          <t>XRD-Rietveld 정량</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -4732,14 +4724,14 @@
       </c>
       <c r="M50" s="15" t="n"/>
       <c r="N50" s="15" t="n">
-        <v>15</v>
+        <v>1.8</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>경험칙 초기값(XRD-Rietveld 정량 기준) — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q50" s="16" t="n"/>
@@ -4751,11 +4743,7 @@
         </is>
       </c>
       <c r="U50" s="10" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr">
-        <is>
-          <t>킬른 산화 분위기·알칼리에서 Cr³⁺ → Cr⁶⁺ 전환(KS L 5221 방법 준용)</t>
-        </is>
-      </c>
+      <c r="V50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -4763,65 +4751,61 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>시멘트(분쇄)</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>cem_blaine</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>시멘트 분말도(Blaine)</t>
+          <t>xrd_periclase</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>XRD 페리클레이스(MgO)</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>cm²/g</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2시간</t>
+          <t>1일</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>XRF·분말도 시험 + DCS(밀 운전)</t>
+          <t>클링커 일일 시료(XRD·크롬, LIMS)</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>KS L 5106(블레인)</t>
+          <t>XRD-Rietveld 정량</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="n">
-        <v>2800</v>
-      </c>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="n"/>
       <c r="K51" s="14" t="n"/>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트</t>
-        </is>
-      </c>
-      <c r="M51" s="15" t="n">
-        <v>3250</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="15" t="n"/>
       <c r="N51" s="15" t="n">
-        <v>3700</v>
+        <v>2</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>3450</v>
+        <v>1</v>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>경험칙 초기값(XRD-Rietveld 정량 기준) — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q51" s="16" t="n"/>
@@ -4829,15 +4813,15 @@
       <c r="S51" s="16" t="n"/>
       <c r="T51" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
-        </is>
-      </c>
-      <c r="U51" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="V51" s="4" t="inlineStr"/>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="U51" s="10" t="inlineStr"/>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>결정질 MgO. 과다 시 오토클레이브 팽창(안정도) 위험</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -4845,61 +4829,57 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>시멘트(분쇄)</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>cem_blaine</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>시멘트 분말도(Blaine)</t>
+          <t>clk_cr</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>클링커 총 크롬</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>cm²/g</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2시간</t>
+          <t>1일</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>XRF·분말도 시험 + DCS(밀 운전)</t>
+          <t>클링커 일일 시료(XRD·크롬, LIMS)</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>KS L 5106(블레인)</t>
+          <t>XRF / ICP(총 크롬)</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
-        </is>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>3300</v>
-      </c>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="n"/>
       <c r="K52" s="14" t="n"/>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트</t>
-        </is>
-      </c>
-      <c r="M52" s="15" t="n">
-        <v>4350</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="15" t="n"/>
       <c r="N52" s="15" t="n">
-        <v>4850</v>
+        <v>120</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>4600</v>
+        <v>65</v>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
@@ -4911,15 +4891,15 @@
       <c r="S52" s="16" t="n"/>
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
-        </is>
-      </c>
-      <c r="U52" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="inlineStr"/>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="U52" s="10" t="inlineStr"/>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>원·부원료·연료·내화물에서 유입된 크롬(XRF/ICP). 6가크롬의 모체</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -4927,42 +4907,42 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>시멘트(분쇄)</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>cem_r45</t>
+          <t>clk_crvi</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>시멘트 45μm 잔사</t>
+          <t>클링커 수용성 Cr⁶⁺</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2시간</t>
+          <t>1일</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>XRF·분말도 시험 + DCS(밀 운전)</t>
+          <t>클링커 일일 시료(XRD·크롬, LIMS)</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L 5221 준용</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>전 품종</t>
         </is>
       </c>
       <c r="J53" s="14" t="n"/>
@@ -4974,10 +4954,10 @@
       </c>
       <c r="M53" s="15" t="n"/>
       <c r="N53" s="15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
@@ -4993,7 +4973,11 @@
         </is>
       </c>
       <c r="U53" s="10" t="inlineStr"/>
-      <c r="V53" s="4" t="inlineStr"/>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>킬른 산화 분위기·알칼리에서 Cr³⁺ → Cr⁶⁺ 전환(KS L 5221 방법 준용)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -5006,17 +4990,17 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>cem_r45</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>시멘트 45μm 잔사</t>
+          <t>cem_blaine</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>시멘트 분말도(Blaine)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>cm²/g</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5031,27 +5015,31 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L 5106(블레인)</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
-        </is>
-      </c>
-      <c r="J54" s="14" t="n"/>
+          <t>1종</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>2800</v>
+      </c>
       <c r="K54" s="14" t="n"/>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트</t>
+        </is>
+      </c>
+      <c r="M54" s="15" t="n">
+        <v>3250</v>
+      </c>
       <c r="N54" s="15" t="n">
-        <v>5</v>
+        <v>3700</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>3</v>
+        <v>3450</v>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
@@ -5063,10 +5051,14 @@
       <c r="S54" s="16" t="n"/>
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="U54" s="10" t="inlineStr"/>
+          <t>R1, R2, R3, R5, R6</t>
+        </is>
+      </c>
+      <c r="U54" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
       <c r="V54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
@@ -5080,17 +5072,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>cem_so3</t>
+          <t>cem_blaine</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>시멘트 SO₃</t>
+          <t>시멘트 분말도(Blaine)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>cm²/g</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5105,31 +5097,31 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>KS L 5120 / XRF</t>
+          <t>KS L 5106(블레인)</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
-        </is>
-      </c>
-      <c r="J55" s="14" t="n"/>
-      <c r="K55" s="14" t="n">
-        <v>3.5</v>
-      </c>
+          <t>3종</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>3300</v>
+      </c>
+      <c r="K55" s="14" t="n"/>
       <c r="L55" s="4" t="inlineStr">
         <is>
           <t>KS L 5201 포틀랜드 시멘트</t>
         </is>
       </c>
       <c r="M55" s="15" t="n">
-        <v>2.3</v>
+        <v>4350</v>
       </c>
       <c r="N55" s="15" t="n">
-        <v>3</v>
+        <v>4850</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>2.6</v>
+        <v>4600</v>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
@@ -5149,11 +5141,7 @@
           <t>●</t>
         </is>
       </c>
-      <c r="V55" s="4" t="inlineStr">
-        <is>
-          <t>석고 최적 SO₃ 이탈 시 강도·응결 변동</t>
-        </is>
-      </c>
+      <c r="V55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -5166,12 +5154,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>cem_so3</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>시멘트 SO₃</t>
+          <t>cem_r45</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>시멘트 45μm 잔사</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -5191,31 +5179,27 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>KS L 5120 / XRF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="K56" s="14" t="n"/>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트</t>
-        </is>
-      </c>
-      <c r="M56" s="15" t="n">
-        <v>2.9</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="15" t="n"/>
       <c r="N56" s="15" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
@@ -5227,19 +5211,11 @@
       <c r="S56" s="16" t="n"/>
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
-        </is>
-      </c>
-      <c r="U56" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="inlineStr">
-        <is>
-          <t>석고 최적 SO₃ 이탈 시 강도·응결 변동</t>
-        </is>
-      </c>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="U56" s="10" t="inlineStr"/>
+      <c r="V56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -5252,12 +5228,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>cem_loi</t>
+          <t>cem_r45</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>시멘트 강열감량</t>
+          <t>시멘트 45μm 잔사</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5277,29 +5253,27 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>KS L 5120</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J57" s="14" t="n"/>
-      <c r="K57" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K57" s="14" t="n"/>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (2016 개정 5.0%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="15" t="n"/>
       <c r="N57" s="15" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
@@ -5328,12 +5302,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>cem_loi</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>시멘트 강열감량</t>
+          <t>cem_so3</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>시멘트 SO₃</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5353,29 +5327,31 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>KS L 5120</t>
+          <t>KS L 5120 / XRF</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J58" s="14" t="n"/>
       <c r="K58" s="14" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (2016 개정 5.0%)</t>
-        </is>
-      </c>
-      <c r="M58" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트</t>
+        </is>
+      </c>
+      <c r="M58" s="15" t="n">
+        <v>2.3</v>
+      </c>
       <c r="N58" s="15" t="n">
         <v>3</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
@@ -5387,11 +5363,19 @@
       <c r="S58" s="16" t="n"/>
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="U58" s="10" t="inlineStr"/>
-      <c r="V58" s="4" t="inlineStr"/>
+          <t>R1, R2, R3, R5, R6</t>
+        </is>
+      </c>
+      <c r="U58" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>석고 최적 SO₃ 이탈 시 강도·응결 변동</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -5404,12 +5388,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>cem_mgo</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>시멘트 MgO</t>
+          <t>cem_so3</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>시멘트 SO₃</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5434,23 +5418,27 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J59" s="14" t="n"/>
       <c r="K59" s="14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
           <t>KS L 5201 포틀랜드 시멘트</t>
         </is>
       </c>
-      <c r="M59" s="15" t="n"/>
+      <c r="M59" s="15" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N59" s="15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O59" s="15" t="n"/>
+        <v>3.6</v>
+      </c>
+      <c r="O59" s="15" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
           <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
@@ -5461,11 +5449,19 @@
       <c r="S59" s="16" t="n"/>
       <c r="T59" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="U59" s="10" t="inlineStr"/>
-      <c r="V59" s="4" t="inlineStr"/>
+          <t>R1, R2, R3, R5, R6</t>
+        </is>
+      </c>
+      <c r="U59" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>석고 최적 SO₃ 이탈 시 강도·응결 변동</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -5478,12 +5474,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>cem_ls</t>
+          <t>cem_loi</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>석회석 혼합률</t>
+          <t>시멘트 강열감량</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5503,7 +5499,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>CO₂·강열감량 역산 / 공급기 실적</t>
+          <t>KS L 5120</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -5512,22 +5508,24 @@
         </is>
       </c>
       <c r="J60" s="14" t="n"/>
-      <c r="K60" s="14" t="n"/>
+      <c r="K60" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L 5201 포틀랜드 시멘트 (2016 개정 5.0%)</t>
         </is>
       </c>
       <c r="M60" s="15" t="n"/>
       <c r="N60" s="15" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 소량 혼합성분 한도(석회석 미분말 5% 등, 2013 개정) — 원문 확인 필요, 사내 상한으로만 관리</t>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q60" s="16" t="n"/>
@@ -5539,11 +5537,7 @@
         </is>
       </c>
       <c r="U60" s="10" t="inlineStr"/>
-      <c r="V60" s="4" t="inlineStr">
-        <is>
-          <t>클링커 희석 → 강도 저하(경험칙: 1%p당 28일 약 0.3~0.5 MPa), 6가크롬 희석 효과</t>
-        </is>
-      </c>
+      <c r="V60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -5556,12 +5550,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>cem_ls</t>
+          <t>cem_loi</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>석회석 혼합률</t>
+          <t>시멘트 강열감량</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5581,7 +5575,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>CO₂·강열감량 역산 / 공급기 실적</t>
+          <t>KS L 5120</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -5590,22 +5584,24 @@
         </is>
       </c>
       <c r="J61" s="14" t="n"/>
-      <c r="K61" s="14" t="n"/>
+      <c r="K61" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L 5201 포틀랜드 시멘트 (2016 개정 5.0%)</t>
         </is>
       </c>
       <c r="M61" s="15" t="n"/>
       <c r="N61" s="15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 소량 혼합성분 한도(석회석 미분말 5% 등, 2013 개정) — 원문 확인 필요, 사내 상한으로만 관리</t>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q61" s="16" t="n"/>
@@ -5617,11 +5613,7 @@
         </is>
       </c>
       <c r="U61" s="10" t="inlineStr"/>
-      <c r="V61" s="4" t="inlineStr">
-        <is>
-          <t>클링커 희석 → 강도 저하(경험칙: 1%p당 28일 약 0.3~0.5 MPa), 6가크롬 희석 효과</t>
-        </is>
-      </c>
+      <c r="V61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -5634,17 +5626,17 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>cem_mill_feed</t>
+          <t>cem_mgo</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>시멘트밀 투입량</t>
+          <t>시멘트 MgO</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -5659,7 +5651,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L 5120 / XRF</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -5668,18 +5660,22 @@
         </is>
       </c>
       <c r="J62" s="14" t="n"/>
-      <c r="K62" s="14" t="n"/>
+      <c r="K62" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L 5201 포틀랜드 시멘트</t>
         </is>
       </c>
       <c r="M62" s="15" t="n"/>
-      <c r="N62" s="15" t="n"/>
+      <c r="N62" s="15" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O62" s="15" t="n"/>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>운전 변수(기준 미설정)</t>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
         </is>
       </c>
       <c r="Q62" s="16" t="n"/>
@@ -5687,7 +5683,7 @@
       <c r="S62" s="16" t="n"/>
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="U62" s="10" t="inlineStr"/>
@@ -5704,17 +5700,17 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>cem_mill_temp</t>
+          <t>cem_ls</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>시멘트밀 출구 온도</t>
+          <t>석회석 혼합률</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -5729,12 +5725,12 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CO₂·강열감량 역산 / 공급기 실적</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J63" s="14" t="n"/>
@@ -5744,18 +5740,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M63" s="15" t="n">
-        <v>90</v>
-      </c>
+      <c r="M63" s="15" t="n"/>
       <c r="N63" s="15" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>KS L 5201 소량 혼합성분 한도(석회석 미분말 5% 등, 2013 개정) — 원문 확인 필요, 사내 상한으로만 관리</t>
         </is>
       </c>
       <c r="Q63" s="16" t="n"/>
@@ -5769,7 +5763,7 @@
       <c r="U63" s="10" t="inlineStr"/>
       <c r="V63" s="4" t="inlineStr">
         <is>
-          <t>과고 시 이수석고 탈수(반수석고화) → 위응결 위험</t>
+          <t>클링커 희석 → 강도 저하(경험칙: 1%p당 28일 약 0.3~0.5 MPa), 6가크롬 희석 효과</t>
         </is>
       </c>
     </row>
@@ -5779,65 +5773,61 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>제품 물성</t>
+          <t>시멘트(분쇄)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>phy_ist</t>
+          <t>cem_ls</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>초결 시간</t>
+          <t>석회석 혼합률</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>물성 시험실(LIMS)</t>
+          <t>XRF·분말도 시험 + DCS(밀 운전)</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>KS L 5108(비카)</t>
+          <t>CO₂·강열감량 역산 / 공급기 실적</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
-        </is>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v>60</v>
-      </c>
+          <t>3종</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="n"/>
       <c r="K64" s="14" t="n"/>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (비카 초결 60분 이상)</t>
-        </is>
-      </c>
-      <c r="M64" s="15" t="n">
-        <v>150</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="15" t="n"/>
       <c r="N64" s="15" t="n">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>220</v>
+        <v>1.5</v>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>KS L 5201 소량 혼합성분 한도(석회석 미분말 5% 등, 2013 개정) — 원문 확인 필요, 사내 상한으로만 관리</t>
         </is>
       </c>
       <c r="Q64" s="16" t="n"/>
@@ -5849,7 +5839,11 @@
         </is>
       </c>
       <c r="U64" s="10" t="inlineStr"/>
-      <c r="V64" s="4" t="inlineStr"/>
+      <c r="V64" s="4" t="inlineStr">
+        <is>
+          <t>클링커 희석 → 강도 저하(경험칙: 1%p당 28일 약 0.3~0.5 MPa), 6가크롬 희석 효과</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -5857,65 +5851,57 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>제품 물성</t>
+          <t>시멘트(분쇄)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>phy_ist</t>
+          <t>cem_mill_feed</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>초결 시간</t>
+          <t>시멘트밀 투입량</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>물성 시험실(LIMS)</t>
+          <t>XRF·분말도 시험 + DCS(밀 운전)</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>KS L 5108(비카)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
-        </is>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v>60</v>
-      </c>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="n"/>
       <c r="K65" s="14" t="n"/>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (비카 초결 60분 이상)</t>
-        </is>
-      </c>
-      <c r="M65" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="N65" s="15" t="n">
-        <v>260</v>
-      </c>
-      <c r="O65" s="15" t="n">
-        <v>180</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="15" t="n"/>
+      <c r="N65" s="15" t="n"/>
+      <c r="O65" s="15" t="n"/>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+          <t>운전 변수(기준 미설정)</t>
         </is>
       </c>
       <c r="Q65" s="16" t="n"/>
@@ -5923,7 +5909,7 @@
       <c r="S65" s="16" t="n"/>
       <c r="T65" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U65" s="10" t="inlineStr"/>
@@ -5935,59 +5921,59 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>제품 물성</t>
+          <t>시멘트(분쇄)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>phy_fst</t>
+          <t>cem_mill_temp</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>종결 시간</t>
+          <t>시멘트밀 출구 온도</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>물성 시험실(LIMS)</t>
+          <t>XRF·분말도 시험 + DCS(밀 운전)</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>KS L 5108(비카)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>전 품종</t>
         </is>
       </c>
       <c r="J66" s="14" t="n"/>
-      <c r="K66" s="14" t="n">
-        <v>600</v>
-      </c>
+      <c r="K66" s="14" t="n"/>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (종결 10시간 이하)</t>
-        </is>
-      </c>
-      <c r="M66" s="15" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="15" t="n">
+        <v>90</v>
+      </c>
       <c r="N66" s="15" t="n">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>300</v>
+        <v>105</v>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
@@ -6003,7 +5989,11 @@
         </is>
       </c>
       <c r="U66" s="10" t="inlineStr"/>
-      <c r="V66" s="4" t="inlineStr"/>
+      <c r="V66" s="4" t="inlineStr">
+        <is>
+          <t>과고 시 이수석고 탈수(반수석고화) → 위응결 위험</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -6016,12 +6006,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>phy_fst</t>
+          <t>phy_ist</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>종결 시간</t>
+          <t>초결 시간</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6046,24 +6036,26 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
-        </is>
-      </c>
-      <c r="J67" s="14" t="n"/>
-      <c r="K67" s="14" t="n">
-        <v>600</v>
-      </c>
+          <t>1종</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K67" s="14" t="n"/>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (종결 10시간 이하)</t>
-        </is>
-      </c>
-      <c r="M67" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트 (비카 초결 60분 이상)</t>
+        </is>
+      </c>
+      <c r="M67" s="15" t="n">
+        <v>150</v>
+      </c>
       <c r="N67" s="15" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
@@ -6092,17 +6084,17 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>phy_autoclave</t>
+          <t>phy_ist</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>오토클레이브 팽창도</t>
+          <t>초결 시간</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>분</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6117,29 +6109,31 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>KS L 5107(오토클레이브)</t>
+          <t>KS L 5108(비카)</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
-        </is>
-      </c>
-      <c r="J68" s="14" t="n"/>
-      <c r="K68" s="14" t="n">
-        <v>0.8</v>
-      </c>
+          <t>3종</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K68" s="14" t="n"/>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (안정도)</t>
-        </is>
-      </c>
-      <c r="M68" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트 (비카 초결 60분 이상)</t>
+        </is>
+      </c>
+      <c r="M68" s="15" t="n">
+        <v>120</v>
+      </c>
       <c r="N68" s="15" t="n">
-        <v>0.3</v>
+        <v>260</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.1</v>
+        <v>180</v>
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
@@ -6168,17 +6162,17 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>phy_crvi</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>시멘트 수용성 6가크롬</t>
+          <t>phy_fst</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>종결 시간</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>분</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -6193,29 +6187,29 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>KS L 5221(수용성 6가크롬)</t>
+          <t>KS L 5108(비카)</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J69" s="14" t="n"/>
       <c r="K69" s="14" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>환경부–시멘트업계 자율협약 20 mg/kg 이하(수용성 Cr⁶⁺, KS L 5221 시험) — 법정 KS 기준 아님, 사내 경고 18</t>
+          <t>KS L 5201 포틀랜드 시멘트 (종결 10시간 이하)</t>
         </is>
       </c>
       <c r="M69" s="15" t="n"/>
       <c r="N69" s="15" t="n">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
@@ -6230,16 +6224,8 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="U69" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="V69" s="4" t="inlineStr">
-        <is>
-          <t>환원제 투입 후 제품값. 국내 자율기준 20 mg/kg, EU 2 mg/kg(EN 196-10, 시험법 상이)</t>
-        </is>
-      </c>
+      <c r="U69" s="10" t="inlineStr"/>
+      <c r="V69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -6252,17 +6238,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>phy_s1</t>
+          <t>phy_fst</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>1일 압축강도</t>
+          <t>종결 시간</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>분</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -6277,7 +6263,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679</t>
+          <t>KS L 5108(비카)</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -6285,21 +6271,21 @@
           <t>3종</t>
         </is>
       </c>
-      <c r="J70" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="K70" s="14" t="n"/>
+      <c r="J70" s="14" t="n"/>
+      <c r="K70" s="14" t="n">
+        <v>600</v>
+      </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트</t>
-        </is>
-      </c>
-      <c r="M70" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="N70" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트 (종결 10시간 이하)</t>
+        </is>
+      </c>
+      <c r="M70" s="15" t="n"/>
+      <c r="N70" s="15" t="n">
+        <v>380</v>
+      </c>
       <c r="O70" s="15" t="n">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
@@ -6311,7 +6297,7 @@
       <c r="S70" s="16" t="n"/>
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="U70" s="10" t="inlineStr"/>
@@ -6328,17 +6314,17 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>phy_s3</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>3일 압축강도</t>
+          <t>phy_autoclave</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>오토클레이브 팽창도</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -6353,29 +6339,29 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679</t>
+          <t>KS L 5107(오토클레이브)</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
-        </is>
-      </c>
-      <c r="J71" s="14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K71" s="14" t="n"/>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="n"/>
+      <c r="K71" s="14" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트</t>
-        </is>
-      </c>
-      <c r="M71" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="N71" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트 (안정도)</t>
+        </is>
+      </c>
+      <c r="M71" s="15" t="n"/>
+      <c r="N71" s="15" t="n">
+        <v>0.3</v>
+      </c>
       <c r="O71" s="15" t="n">
-        <v>29.5</v>
+        <v>0.1</v>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
@@ -6387,14 +6373,10 @@
       <c r="S71" s="16" t="n"/>
       <c r="T71" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
-        </is>
-      </c>
-      <c r="U71" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="U71" s="10" t="inlineStr"/>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
@@ -6408,17 +6390,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>phy_s3</t>
+          <t>phy_crvi</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>3일 압축강도</t>
+          <t>시멘트 수용성 6가크롬</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -6433,29 +6415,29 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679</t>
+          <t>KS L 5221(수용성 6가크롬)</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
-        </is>
-      </c>
-      <c r="J72" s="14" t="n">
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="K72" s="14" t="n"/>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="N72" s="15" t="n"/>
+          <t>환경부–시멘트업계 자율협약 20 mg/kg 이하(수용성 Cr⁶⁺, KS L 5221 시험) — 법정 KS 기준 아님, 사내 경고 18</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="15" t="n">
+        <v>18</v>
+      </c>
       <c r="O72" s="15" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
@@ -6467,7 +6449,7 @@
       <c r="S72" s="16" t="n"/>
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t>R1, R2, R3, R5, R6</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="U72" s="10" t="inlineStr">
@@ -6475,7 +6457,11 @@
           <t>●</t>
         </is>
       </c>
-      <c r="V72" s="4" t="inlineStr"/>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>환원제 투입 후 제품값. 국내 자율기준 20 mg/kg, EU 2 mg/kg(EN 196-10, 시험법 상이)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -6488,12 +6474,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>phy_s7</t>
-        </is>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>7일 압축강도</t>
+          <t>phy_s1</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>1일 압축강도</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6518,11 +6504,11 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J73" s="14" t="n">
-        <v>22.5</v>
+        <v>10</v>
       </c>
       <c r="K73" s="14" t="n"/>
       <c r="L73" s="4" t="inlineStr">
@@ -6531,11 +6517,11 @@
         </is>
       </c>
       <c r="M73" s="15" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="N73" s="15" t="n"/>
       <c r="O73" s="15" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
@@ -6550,11 +6536,7 @@
           <t>R1, R2, R3, R5, R6</t>
         </is>
       </c>
-      <c r="U73" s="10" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="U73" s="10" t="inlineStr"/>
       <c r="V73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
@@ -6568,12 +6550,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>phy_s7</t>
+          <t>phy_s3</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>7일 압축강도</t>
+          <t>3일 압축강도</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -6598,11 +6580,11 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>32.5</v>
+        <v>12.5</v>
       </c>
       <c r="K74" s="14" t="n"/>
       <c r="L74" s="4" t="inlineStr">
@@ -6611,11 +6593,11 @@
         </is>
       </c>
       <c r="M74" s="15" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N74" s="15" t="n"/>
       <c r="O74" s="15" t="n">
-        <v>46</v>
+        <v>29.5</v>
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
@@ -6648,12 +6630,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>phy_s28</t>
+          <t>phy_s3</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>28일 압축강도</t>
+          <t>3일 압축강도</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -6678,11 +6660,11 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J75" s="14" t="n">
-        <v>42.5</v>
+        <v>20</v>
       </c>
       <c r="K75" s="14" t="n"/>
       <c r="L75" s="4" t="inlineStr">
@@ -6691,11 +6673,11 @@
         </is>
       </c>
       <c r="M75" s="15" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="N75" s="15" t="n"/>
       <c r="O75" s="15" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
@@ -6728,12 +6710,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>phy_s28</t>
+          <t>phy_s7</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>28일 압축강도</t>
+          <t>7일 압축강도</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -6758,11 +6740,11 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>47.5</v>
+        <v>22.5</v>
       </c>
       <c r="K76" s="14" t="n"/>
       <c r="L76" s="4" t="inlineStr">
@@ -6771,11 +6753,11 @@
         </is>
       </c>
       <c r="M76" s="15" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="N76" s="15" t="n"/>
       <c r="O76" s="15" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
@@ -6808,12 +6790,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>pred_s28</t>
+          <t>phy_s7</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>28일 강도(예측)</t>
+          <t>7일 압축강도</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -6833,29 +6815,29 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L ISO 679</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J77" s="14" t="n">
-        <v>42.5</v>
+        <v>32.5</v>
       </c>
       <c r="K77" s="14" t="n"/>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (예측값 — 실측 확인 필요)</t>
+          <t>KS L 5201 포틀랜드 시멘트</t>
         </is>
       </c>
       <c r="M77" s="15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N77" s="15" t="n"/>
       <c r="O77" s="15" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
@@ -6867,7 +6849,7 @@
       <c r="S77" s="16" t="n"/>
       <c r="T77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R1, R2, R3, R5, R6</t>
         </is>
       </c>
       <c r="U77" s="10" t="inlineStr">
@@ -6875,11 +6857,7 @@
           <t>●</t>
         </is>
       </c>
-      <c r="V77" s="4" t="inlineStr">
-        <is>
-          <t>조기 강도·화학 성분으로 회귀 예측. 28일 결과 전 조기 경보용</t>
-        </is>
-      </c>
+      <c r="V77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -6892,12 +6870,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>pred_s28</t>
+          <t>phy_s28</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>28일 강도(예측)</t>
+          <t>28일 압축강도</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -6917,29 +6895,29 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KS L ISO 679</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>3종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>47.5</v>
+        <v>42.5</v>
       </c>
       <c r="K78" s="14" t="n"/>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>KS L 5201 포틀랜드 시멘트 (예측값 — 실측 확인 필요)</t>
+          <t>KS L 5201 포틀랜드 시멘트</t>
         </is>
       </c>
       <c r="M78" s="15" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N78" s="15" t="n"/>
       <c r="O78" s="15" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
@@ -6951,7 +6929,7 @@
       <c r="S78" s="16" t="n"/>
       <c r="T78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R1, R2, R3, R5, R6</t>
         </is>
       </c>
       <c r="U78" s="10" t="inlineStr">
@@ -6959,11 +6937,7 @@
           <t>●</t>
         </is>
       </c>
-      <c r="V78" s="4" t="inlineStr">
-        <is>
-          <t>조기 강도·화학 성분으로 회귀 예측. 28일 결과 전 조기 경보용</t>
-        </is>
-      </c>
+      <c r="V78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -6971,22 +6945,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>시험 조건</t>
+          <t>제품 물성</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>lab_temp</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>시험실 온도</t>
+          <t>phy_s28</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>28일 압축강도</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -7006,24 +6980,24 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J79" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K79" s="14" t="n">
-        <v>22</v>
-      </c>
+        <v>47.5</v>
+      </c>
+      <c r="K79" s="14" t="n"/>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679 강도 시험방법(ISO 679 시험조건) 20±2℃</t>
-        </is>
-      </c>
-      <c r="M79" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="n">
+        <v>54</v>
+      </c>
       <c r="N79" s="15" t="n"/>
       <c r="O79" s="15" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
@@ -7035,10 +7009,14 @@
       <c r="S79" s="16" t="n"/>
       <c r="T79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U79" s="10" t="inlineStr"/>
+          <t>R1, R2, R3, R5, R6</t>
+        </is>
+      </c>
+      <c r="U79" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
       <c r="V79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
@@ -7047,22 +7025,22 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>시험 조건</t>
+          <t>제품 물성</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>lab_rh</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>시험실 상대습도</t>
+          <t>pred_s28</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>28일 강도(예측)</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -7077,26 +7055,30 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
+          <t>1종</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679 강도 시험방법(ISO 679 시험조건) 50% 이상</t>
-        </is>
-      </c>
-      <c r="M80" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트 (예측값 — 실측 확인 필요)</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="n">
+        <v>48</v>
+      </c>
       <c r="N80" s="15" t="n"/>
-      <c r="O80" s="15" t="n"/>
+      <c r="O80" s="15" t="n">
+        <v>53</v>
+      </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
           <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
@@ -7110,8 +7092,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U80" s="10" t="inlineStr"/>
-      <c r="V80" s="4" t="inlineStr"/>
+      <c r="U80" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="V80" s="4" t="inlineStr">
+        <is>
+          <t>조기 강도·화학 성분으로 회귀 예측. 28일 결과 전 조기 경보용</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -7119,22 +7109,22 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>시험 조건</t>
+          <t>제품 물성</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>lab_cure_temp</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>양생수 온도</t>
+          <t>pred_s28</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>28일 강도(예측)</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -7149,29 +7139,29 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>전 품종</t>
+          <t>3종</t>
         </is>
       </c>
       <c r="J81" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="K81" s="14" t="n">
-        <v>21</v>
-      </c>
+        <v>47.5</v>
+      </c>
+      <c r="K81" s="14" t="n"/>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>KS L ISO 679 강도 시험방법(ISO 679 시험조건) 20±1℃</t>
-        </is>
-      </c>
-      <c r="M81" s="15" t="n"/>
+          <t>KS L 5201 포틀랜드 시멘트 (예측값 — 실측 확인 필요)</t>
+        </is>
+      </c>
+      <c r="M81" s="15" t="n">
+        <v>54</v>
+      </c>
       <c r="N81" s="15" t="n"/>
       <c r="O81" s="15" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
@@ -7186,13 +7176,245 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U81" s="10" t="inlineStr"/>
-      <c r="V81" s="4" t="inlineStr"/>
+      <c r="U81" s="10" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="V81" s="4" t="inlineStr">
+        <is>
+          <t>조기 강도·화학 성분으로 회귀 예측. 28일 결과 전 조기 경보용</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>시험 조건</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>lab_temp</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>시험실 온도</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>물성 시험실(LIMS)</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>KS L ISO 679</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="K82" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>KS L ISO 679 강도 시험방법(ISO 679 시험조건) 20±2℃</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="n"/>
+      <c r="N82" s="15" t="n"/>
+      <c r="O82" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="P82" s="4" t="inlineStr">
+        <is>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+        </is>
+      </c>
+      <c r="Q82" s="16" t="n"/>
+      <c r="R82" s="16" t="n"/>
+      <c r="S82" s="16" t="n"/>
+      <c r="T82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U82" s="10" t="inlineStr"/>
+      <c r="V82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>시험 조건</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>lab_rh</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>시험실 상대습도</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>물성 시험실(LIMS)</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>KS L ISO 679</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="K83" s="14" t="n"/>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>KS L ISO 679 강도 시험방법(ISO 679 시험조건) 50% 이상</t>
+        </is>
+      </c>
+      <c r="M83" s="15" t="n"/>
+      <c r="N83" s="15" t="n"/>
+      <c r="O83" s="15" t="n"/>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+        </is>
+      </c>
+      <c r="Q83" s="16" t="n"/>
+      <c r="R83" s="16" t="n"/>
+      <c r="S83" s="16" t="n"/>
+      <c r="T83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U83" s="10" t="inlineStr"/>
+      <c r="V83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>시험 조건</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>lab_cure_temp</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>양생수 온도</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>물성 시험실(LIMS)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>KS L ISO 679</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>전 품종</t>
+        </is>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="K84" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>KS L ISO 679 강도 시험방법(ISO 679 시험조건) 20±1℃</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="n"/>
+      <c r="N84" s="15" t="n"/>
+      <c r="O84" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>경험칙 초기값 — 공장 기준으로 교체 필요</t>
+        </is>
+      </c>
+      <c r="Q84" s="16" t="n"/>
+      <c r="R84" s="16" t="n"/>
+      <c r="S84" s="16" t="n"/>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U84" s="10" t="inlineStr"/>
+      <c r="V84" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V81"/>
+  <autoFilter ref="A1:V84"/>
   <dataValidations count="1">
-    <dataValidation sqref="Q2:S81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="숫자만 입력하세요(단위 제외)." type="decimal" operator="between">
+    <dataValidation sqref="Q2:S84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="숫자만 입력하세요(단위 제외)." type="decimal" operator="between">
       <formula1>-100000</formula1>
       <formula2>100000</formula2>
     </dataValidation>
@@ -16384,7 +16606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16467,17 +16689,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>rm_cao</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>원료 CaO</t>
+          <t>line</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -16499,17 +16721,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>rm_sio2</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>원료 SiO₂</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -16531,12 +16753,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>rm_al2o3</t>
+          <t>rm_cao</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>원료 Al₂O₃</t>
+          <t>원료 CaO</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -16563,12 +16785,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>rm_fe2o3</t>
+          <t>rm_sio2</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>원료 Fe₂O₃</t>
+          <t>원료 SiO₂</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -16595,12 +16817,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>rm_mgo</t>
+          <t>rm_al2o3</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>원료 MgO</t>
+          <t>원료 Al₂O₃</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -16627,12 +16849,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>rm_so3</t>
+          <t>rm_fe2o3</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>원료 SO₃</t>
+          <t>원료 Fe₂O₃</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -16659,12 +16881,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>rm_k2o</t>
+          <t>rm_mgo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>원료 K₂O</t>
+          <t>원료 MgO</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -16691,12 +16913,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>rm_na2o</t>
+          <t>rm_so3</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>원료 Na₂O</t>
+          <t>원료 SO₃</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -16723,12 +16945,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>rm_r90</t>
+          <t>rm_k2o</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>원료 90μm 잔사</t>
+          <t>원료 K₂O</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -16755,12 +16977,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>rm_r200</t>
+          <t>rm_na2o</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>원료 200μm 잔사</t>
+          <t>원료 Na₂O</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -16787,12 +17009,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>rm_loi</t>
+          <t>rm_r90</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>원료 강열감량</t>
+          <t>원료 90μm 잔사</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -16819,17 +17041,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_lime</t>
+          <t>rm_r200</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_lime</t>
+          <t>원료 200μm 잔사</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -16851,17 +17073,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_shale</t>
+          <t>rm_loi</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_shale</t>
+          <t>원료 강열감량</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -16883,12 +17105,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_silica</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_silica</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -16915,12 +17137,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_silica2</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_silica2</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -16947,12 +17169,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_ash</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_ash</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -16979,12 +17201,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_sago</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_sago</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -17011,12 +17233,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_iron</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_iron</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -17043,12 +17265,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_sand</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_sand</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -17075,12 +17297,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_total</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>rm_mx_total</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -17102,17 +17324,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>킬른</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>측정일시(예: 2026-10-07 14:00)</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -17122,39 +17344,39 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>1시간</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>킬른</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>kiln_feed</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>원료 투입량</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1시간</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -17171,17 +17393,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>coal_rate</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>석탄 투입량</t>
+          <t>측정일시(예: 2026-10-07 14:00)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -17191,7 +17413,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
     </row>
@@ -17203,17 +17425,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>kiln_bzt</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>소성대 온도(파이로미터)</t>
+          <t>line</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -17235,17 +17457,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>kiln_o2</t>
+          <t>kiln_feed</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>킬른 입구 O₂</t>
+          <t>원료 투입량</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -17267,17 +17489,17 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>kiln_co</t>
+          <t>coal_rate</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>킬른 입구 CO</t>
+          <t>석탄 투입량</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -17299,17 +17521,17 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>kiln_torque</t>
+          <t>kiln_bzt</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>킬른 주모터 부하</t>
+          <t>소성대 온도(파이로미터)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -17331,17 +17553,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>kiln_calc_temp</t>
+          <t>kiln_o2</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>하소로 출구 온도</t>
+          <t>킬른 입구 O₂</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -17363,17 +17585,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>kiln_sec_air</t>
+          <t>kiln_co</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2차 공기 온도</t>
+          <t>킬른 입구 CO</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -17390,59 +17612,59 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>킬른</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>kiln_torque</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>측정일시(예: 2026-10-07 14:00)</t>
+          <t>킬른 주모터 부하</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2시간</t>
+          <t>1시간</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>킬른</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>clk_cao</t>
+          <t>kiln_calc_temp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>하소로 출구 온도</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2시간</t>
+          <t>1시간</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -17454,27 +17676,27 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>킬른</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>clk_sio2</t>
+          <t>kiln_sec_air</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>클링커 SiO₂</t>
+          <t>2차 공기 온도</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2시간</t>
+          <t>1시간</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -17491,17 +17713,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>clk_al2o3</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>클링커 Al₂O₃</t>
+          <t>측정일시(예: 2026-10-07 14:00)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -17511,7 +17733,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
     </row>
@@ -17523,17 +17745,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>clk_fe2o3</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>클링커 Fe₂O₃</t>
+          <t>line</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -17555,17 +17777,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>clk_mgo</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -17587,17 +17809,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>clk_so3</t>
+          <t>silo</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>클링커 SO₃</t>
+          <t>silo</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -17619,12 +17841,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>clk_k2o</t>
+          <t>clk_cao</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>클링커 K₂O</t>
+          <t>클링커 CaO</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -17651,12 +17873,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>clk_na2o</t>
+          <t>clk_sio2</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>클링커 Na₂O</t>
+          <t>클링커 SiO₂</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -17683,12 +17905,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>clk_fcao</t>
+          <t>clk_al2o3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>클링커 자유석회(f-CaO)</t>
+          <t>클링커 Al₂O₃</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -17715,17 +17937,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>clk_lw</t>
+          <t>clk_fe2o3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>클링커 리터중량</t>
+          <t>클링커 Fe₂O₃</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>g/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -17742,22 +17964,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>clk_mgo</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>측정일시(예: 2026-10-07 14:00)</t>
+          <t>클링커 MgO</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -17767,29 +17989,29 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>clk_so3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>품종(1종/3종)</t>
+          <t>클링커 SO₃</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -17799,29 +18021,29 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>cem_blaine</t>
+          <t>clk_k2o</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>시멘트 분말도(Blaine)</t>
+          <t>클링커 K₂O</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>cm²/g</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -17838,17 +18060,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>cem_r45</t>
+          <t>clk_na2o</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>시멘트 45μm 잔사</t>
+          <t>클링커 Na₂O</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -17870,17 +18092,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>cem_so3</t>
+          <t>clk_fcao</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>시멘트 SO₃</t>
+          <t>클링커 자유석회(f-CaO)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -17902,22 +18124,22 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>cem_loi</t>
+          <t>clk_lw</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>시멘트 강열감량</t>
+          <t>클링커 리터중량</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>g/L</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -17934,22 +18156,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>cem_mgo</t>
+          <t>clk_cl</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>시멘트 MgO</t>
+          <t>클링커 Cl</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -17966,22 +18188,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>cem_ls</t>
+          <t>clk_f</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>석회석 혼합률</t>
+          <t>클링커 F</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ppm</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -17998,22 +18220,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>cem_mill_feed</t>
+          <t>clk_temp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>시멘트밀 투입량</t>
+          <t>클링커 온도</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -18035,17 +18257,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>cem_mill_temp</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>시멘트밀 출구 온도</t>
+          <t>측정일시(예: 2026-10-07 14:00)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -18055,7 +18277,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
     </row>
@@ -18067,12 +18289,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cem_cao</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>cem_cao</t>
+          <t>line</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -18099,12 +18321,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>cem_sio2</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>cem_sio2</t>
+          <t>품종(1종/3종)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -18119,7 +18341,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
     </row>
@@ -18131,12 +18353,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>cem_al2o3</t>
+          <t>silo</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>cem_al2o3</t>
+          <t>silo</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -18163,17 +18385,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>cem_fe2o3</t>
+          <t>cem_blaine</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>cem_fe2o3</t>
+          <t>시멘트 분말도(Blaine)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>cm²/g</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -18195,17 +18417,17 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>cem_na2o</t>
+          <t>cem_r45</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>cem_na2o</t>
+          <t>시멘트 45μm 잔사</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -18227,17 +18449,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>cem_k2o</t>
+          <t>cem_so3</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>cem_k2o</t>
+          <t>시멘트 SO₃</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -18259,17 +18481,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>cem_cl</t>
+          <t>cem_loi</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>cem_cl</t>
+          <t>시멘트 강열감량</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -18291,17 +18513,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>cem_fcao</t>
+          <t>cem_mgo</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>cem_fcao</t>
+          <t>시멘트 MgO</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -18318,91 +18540,91 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>cem_ls</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>측정일시(예: 2026-10-07 14:00)</t>
+          <t>석회석 혼합률</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>cem_mill_feed</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>품종(1종/3종)</t>
+          <t>시멘트밀 투입량</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>phy_ist</t>
+          <t>cem_mill_temp</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>초결 시간</t>
+          <t>시멘트밀 출구 온도</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -18414,27 +18636,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>phy_fst</t>
+          <t>cem_cao</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>종결 시간</t>
+          <t>cem_cao</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -18446,27 +18668,27 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>phy_autoclave</t>
+          <t>cem_sio2</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>오토클레이브 팽창도</t>
+          <t>cem_sio2</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -18478,27 +18700,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>phy_s1</t>
+          <t>cem_al2o3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1일 압축강도</t>
+          <t>cem_al2o3</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -18510,27 +18732,27 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>phy_s3</t>
+          <t>cem_fe2o3</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>3일 압축강도</t>
+          <t>cem_fe2o3</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -18542,27 +18764,27 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>phy_s7</t>
+          <t>cem_na2o</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7일 압축강도</t>
+          <t>cem_na2o</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -18574,27 +18796,27 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>phy_s28</t>
+          <t>cem_k2o</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>28일 압축강도</t>
+          <t>cem_k2o</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -18606,27 +18828,27 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>phy_crvi</t>
+          <t>cem_cl</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>시멘트 수용성 6가크롬</t>
+          <t>cem_cl</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -18638,27 +18860,27 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>물성</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>lab_temp</t>
+          <t>cem_fcao</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>시험실 온도</t>
+          <t>cem_fcao</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>1일</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -18675,17 +18897,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>lab_rh</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>시험실 상대습도</t>
+          <t>측정일시(예: 2026-10-07 14:00)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -18695,7 +18917,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
     </row>
@@ -18707,17 +18929,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>lab_cure_temp</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>양생수 온도</t>
+          <t>품종(1종/3종)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -18727,7 +18949,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
     </row>
@@ -18739,17 +18961,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>sand_lot</t>
+          <t>phy_ist</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>표준사 Lot</t>
+          <t>초결 시간</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>분</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -18771,17 +18993,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>operator</t>
+          <t>phy_fst</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>시험 조</t>
+          <t>종결 시간</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>분</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -18798,22 +19020,22 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>phy_autoclave</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>측정일시(예: 2026-10-07 14:00)</t>
+          <t>오토클레이브 팽창도</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -18823,29 +19045,29 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>필수</t>
+          <t>선택</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>xrd_alite</t>
+          <t>phy_s1</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>XRD 알라이트(C₃S)</t>
+          <t>1일 압축강도</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -18862,22 +19084,22 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>xrd_belite</t>
+          <t>phy_s3</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>XRD 벨라이트(C₂S)</t>
+          <t>3일 압축강도</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -18894,22 +19116,22 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>xrd_c3a</t>
+          <t>phy_s7</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>XRD C₃A(입방+사방)</t>
+          <t>7일 압축강도</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -18926,22 +19148,22 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>xrd_c4af</t>
+          <t>phy_s28</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>XRD 페라이트(C₄AF)</t>
+          <t>28일 압축강도</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -18958,22 +19180,22 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>xrd_fcao</t>
+          <t>phy_crvi</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>XRD 자유석회</t>
+          <t>시멘트 수용성 6가크롬</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -18990,22 +19212,22 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>xrd_periclase</t>
+          <t>lab_temp</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>XRD 페리클레이스(MgO)</t>
+          <t>시험실 온도</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -19022,22 +19244,22 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>클링커일일</t>
+          <t>물성</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>clk_cr</t>
+          <t>lab_rh</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>클링커 총 크롬</t>
+          <t>시험실 상대습도</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -19054,37 +19276,453 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
+          <t>물성</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>lab_cure_temp</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>양생수 온도</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>물성</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>sand_lot</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>표준사 Lot</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>물성</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>operator</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>시험 조</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
           <t>클링커일일</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>측정일시(예: 2026-10-07 14:00)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>xrd_alite</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>XRD 알라이트(C₃S)</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>xrd_belite</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>XRD 벨라이트(C₂S)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>xrd_c3a</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>XRD C₃A(입방+사방)</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>xrd_c4af</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>XRD 페라이트(C₄AF)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>xrd_fcao</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>XRD 자유석회</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>xrd_periclase</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>XRD 페리클레이스(MgO)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>clk_cr</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>클링커 총 크롬</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>클링커일일</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>clk_crvi</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>클링커 수용성 Cr⁶⁺</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>1일</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>※ LSF·SM·IM·C₃S·액상량 등 파생값은 시스템이 자동 계산하므로 입력하지 않음. 같은 측정일시(+품종)는 값이 있는 칸만 덮어씀(빈 칸은 기존 값 유지 — LIMS 결과 순차 반영).</t>
         </is>
